--- a/data/trans_bre/IMC_inf_MED_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 26,05</t>
+          <t>-18,8; 25,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 16,61</t>
+          <t>-26,68; 16,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-52,36; 8,28</t>
+          <t>-53,05; 8,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 63,69</t>
+          <t>-29,27; 61,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 38,37</t>
+          <t>-41,8; 38,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-77,97; 30,55</t>
+          <t>-80,38; 26,79</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,14; -3,83</t>
+          <t>-20,01; -3,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,55; -2,15</t>
+          <t>-19,09; -2,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 6,17</t>
+          <t>-21,03; 6,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -6,75</t>
+          <t>-30,57; -6,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,2; -4,71</t>
+          <t>-35,7; -4,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,35; 14,78</t>
+          <t>-39,17; 15,78</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 10,14</t>
+          <t>-10,55; 9,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,84; -3,46</t>
+          <t>-23,38; -4,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 10,08</t>
+          <t>-17,78; 11,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 20,93</t>
+          <t>-18,32; 20,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,35; -7,39</t>
+          <t>-41,96; -10,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 26,27</t>
+          <t>-35,89; 31,11</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,21; -6,03</t>
+          <t>-23,76; -5,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 0,91</t>
+          <t>-15,66; 1,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,3; -7,26</t>
+          <t>-32,32; -6,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,59; -15,32</t>
+          <t>-52,48; -15,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 3,33</t>
+          <t>-43,28; 8,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,78; -27,44</t>
+          <t>-81,82; -23,91</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -4,07</t>
+          <t>-13,83; -3,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -5,62</t>
+          <t>-15,46; -5,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,25; -4,79</t>
+          <t>-22,81; -4,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,96; -7,88</t>
+          <t>-24,72; -6,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,25; -13,07</t>
+          <t>-32,46; -13,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,09; -13,85</t>
+          <t>-54,39; -13,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Edad-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 25,6</t>
+          <t>-16,33; 23,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,68; 16,24</t>
+          <t>-27,65; 13,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-53,05; 8,42</t>
+          <t>-51,09; 8,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 61,26</t>
+          <t>-25,24; 59,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 38,77</t>
+          <t>-44,77; 34,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,38; 26,79</t>
+          <t>-78,65; 34,31</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,01; -3,89</t>
+          <t>-20,42; -3,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,09; -2,11</t>
+          <t>-18,44; -2,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 6,96</t>
+          <t>-21,59; 7,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,57; -6,74</t>
+          <t>-30,62; -6,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,7; -4,84</t>
+          <t>-34,87; -5,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,17; 15,78</t>
+          <t>-38,56; 18,91</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 9,9</t>
+          <t>-10,35; 10,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,38; -4,58</t>
+          <t>-21,95; -4,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 11,67</t>
+          <t>-19,81; 11,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 20,67</t>
+          <t>-17,07; 21,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,96; -10,22</t>
+          <t>-40,72; -7,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,89; 31,11</t>
+          <t>-39,11; 31,61</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,76; -5,61</t>
+          <t>-23,49; -5,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 1,65</t>
+          <t>-17,22; 1,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -6,4</t>
+          <t>-30,42; -6,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,48; -15,33</t>
+          <t>-51,93; -15,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,28; 8,1</t>
+          <t>-45,8; 5,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,82; -23,91</t>
+          <t>-79,81; -25,13</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,83; -3,64</t>
+          <t>-13,42; -3,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -5,62</t>
+          <t>-15,46; -5,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,81; -4,82</t>
+          <t>-22,53; -4,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,72; -6,86</t>
+          <t>-23,66; -7,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -13,35</t>
+          <t>-32,44; -12,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-54,39; -13,64</t>
+          <t>-51,72; -12,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-22,16</t>
+          <t>-24,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-43,47%</t>
+          <t>-45,28%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 23,71</t>
+          <t>-16,59; 26,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 13,6</t>
+          <t>-27,42; 16,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-51,09; 8,85</t>
+          <t>-53,86; 6,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 59,31</t>
+          <t>-25,71; 63,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 34,08</t>
+          <t>-44,31; 38,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-78,65; 34,31</t>
+          <t>-78,03; 26,5</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-7,78</t>
+          <t>-9,37</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,37%</t>
+          <t>-18,83%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,42; -3,33</t>
+          <t>-20,14; -3,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -2,46</t>
+          <t>-18,55; -2,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 7,7</t>
+          <t>-23,87; 4,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,62; -6,29</t>
+          <t>-30,39; -6,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,87; -5,36</t>
+          <t>-34,2; -4,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 18,91</t>
+          <t>-43,83; 8,92</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-6,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,19%</t>
+          <t>-15,35%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 10,1</t>
+          <t>-9,86; 10,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,95; -4,14</t>
+          <t>-22,84; -3,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 11,91</t>
+          <t>-20,0; 6,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 21,05</t>
+          <t>-17,27; 20,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,72; -7,69</t>
+          <t>-41,35; -7,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,11; 31,61</t>
+          <t>-39,82; 14,64</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-18,26</t>
+          <t>-17,57</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-57,49%</t>
+          <t>-54,33%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,49; -5,92</t>
+          <t>-23,21; -6,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 1,21</t>
+          <t>-16,62; 0,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,42; -6,16</t>
+          <t>-30,4; -7,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,93; -15,83</t>
+          <t>-50,59; -15,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,8; 5,58</t>
+          <t>-44,11; 3,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,81; -25,13</t>
+          <t>-74,53; -25,14</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-13,31</t>
+          <t>-13,11</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-32,43%</t>
+          <t>-31,92%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,42; -3,61</t>
+          <t>-14,05; -4,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -5,53</t>
+          <t>-15,38; -5,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -4,37</t>
+          <t>-20,59; -6,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,66; -7,08</t>
+          <t>-24,96; -7,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,44; -12,72</t>
+          <t>-32,25; -13,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -12,58</t>
+          <t>-45,71; -16,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,28</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,99</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-24,75</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-12,92%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-45,28%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.283890730163331</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-6.99039268752617</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-24.75012685175494</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.07929278561026033</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1291920403208148</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4527582552893388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-16,59; 26,05</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-27,42; 16,61</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-53,86; 6,9</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-25,71; 63,69</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-44,31; 38,37</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-78,03; 26,5</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-16.58518987176517</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-27.42129136727126</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-53.85536130797725</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.2571407245229286</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4430673208664155</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.7802814273533686</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>26.05019715822507</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>16.60518025864002</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.898732089609523</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.6368546076120918</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3836687347979095</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2649654336199797</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-11,76</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-10,61</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-9,37</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-18,71%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-21,38%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-18,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-20,14; -3,83</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-18,55; -2,15</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-23,87; 4,08</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-30,39; -6,75</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-34,2; -4,71</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-43,83; 8,92</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-11.76493339318079</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-10.61174410460822</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-9.370667561332002</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1870834737200991</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2137955336343386</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1883299108199978</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-13,5</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-6,93</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-26,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-15,35%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-20.13982821676423</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-18.55427960058357</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-23.87046932062614</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.3038617423961108</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3419949823602058</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4383331352227154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,86; 10,14</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-22,84; -3,46</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-20,0; 6,3</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-17,27; 20,93</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-41,35; -7,39</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-39,82; 14,64</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-3.833562881173728</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-2.150177887578737</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.083134757062313</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.06748188495051413</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.04708779667646686</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.08918629246246057</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +767,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-14,36</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-7,66</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-17,57</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-34,69%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-23,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-54,33%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.1781391915491093</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-13.49536188571536</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-6.925229889106871</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.003331774705441797</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2647188215110544</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1534844415819098</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-23,21; -6,03</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-16,62; 0,91</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-30,4; -7,28</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-50,59; -15,32</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-44,11; 3,33</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-74,53; -25,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.864043739585366</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-22.83988672245083</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-20.0025163841903</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.1727318936606963</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4135009773195613</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3981928662649488</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.14346606388379</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-3.464731914823332</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.301075093199633</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.2093451501930489</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.07393440111953362</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1463506475196255</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-14.35951226301108</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-7.663522930678604</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-17.57230751240032</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3469170021963952</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2386557515331303</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.5433488791702172</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-23.21243653102392</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-16.619274532272</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-30.39707156607484</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.5059151585536504</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4410763122043909</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7453411786641653</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-6.026714880504888</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9128541708607949</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-7.279675619616619</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.1531757562215723</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.03331586094325876</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.2513664151310048</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-8,65</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-10,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-13,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-16,1%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-23,31%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-31,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-14,05; -4,07</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-15,38; -5,62</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-20,59; -6,23</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-24,96; -7,88</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-32,25; -13,07</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-45,71; -16,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-8.646016862266686</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-10.57482590979102</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-13.11358105237744</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.1610404554092529</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2331172834798522</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.3191600958763511</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-14.05485157358868</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-15.3838240810823</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-20.59297094299193</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.2495733593773561</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3225077584074911</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.457093758520137</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-4.067695096038559</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-5.620049701465927</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-6.229699311760297</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-0.07875899032385812</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-0.1306902523445392</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-0.1605174301198594</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +1012,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_bre/IMC_inf_MED_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Edad-trans_bre.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>4.283890730163331</v>
+        <v>13.08883983087371</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-6.99039268752617</v>
+        <v>-3.0381313792885</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>-24.75012685175494</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.07929278561026033</v>
+        <v>0.2997179011816251</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.1291920403208148</v>
+        <v>-0.05982712654717547</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>-0.4527582552893388</v>
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-16.58518987176517</v>
+        <v>-7.686212940100592</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-27.42129136727126</v>
+        <v>-23.22201037854331</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>-53.85536130797725</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.2571407245229286</v>
+        <v>-0.1259207034037145</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.4430673208664155</v>
+        <v>-0.3742422980934859</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>-0.7802814273533686</v>
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>26.05019715822507</v>
+        <v>29.76443857006841</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>16.60518025864002</v>
+        <v>15.51856724113869</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6.898732089609523</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.6368546076120918</v>
+        <v>0.9266911219347044</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.3836687347979095</v>
+        <v>0.4024501096621688</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.2649654336199797</v>
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-11.76493339318079</v>
+        <v>-8.7568112152408</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-10.61174410460822</v>
+        <v>-8.997651865935218</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-9.370667561332002</v>
+        <v>-7.342074702343643</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1870834737200991</v>
+        <v>-0.1467242809906736</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2137955336343386</v>
+        <v>-0.1879881242707817</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.1883299108199978</v>
+        <v>-0.1496034264479479</v>
       </c>
     </row>
     <row r="8">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-20.13982821676423</v>
+        <v>-15.88076041163241</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-18.55427960058357</v>
+        <v>-15.81698579064084</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-23.87046932062614</v>
+        <v>-21.09687335217868</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.3038617423961108</v>
+        <v>-0.2543645827285623</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.3419949823602058</v>
+        <v>-0.3124908083214422</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.4383331352227154</v>
+        <v>-0.3785761154488749</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-3.833562881173728</v>
+        <v>-1.732541277053649</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-2.150177887578737</v>
+        <v>-1.380369507295433</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4.083134757062313</v>
+        <v>7.109962328078727</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.06748188495051413</v>
+        <v>-0.03050705360741992</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.04708779667646686</v>
+        <v>-0.03052124418610881</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.08918629246246057</v>
+        <v>0.165218531694116</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.1781391915491093</v>
+        <v>-3.409577963851829</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-13.49536188571536</v>
+        <v>-13.9889896863728</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-6.925229889106871</v>
+        <v>-5.629932464293585</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.003331774705441797</v>
+        <v>-0.06266428971095694</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.2647188215110544</v>
+        <v>-0.2775219113921931</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.1534844415819098</v>
+        <v>-0.1253138406413549</v>
       </c>
     </row>
     <row r="11">
@@ -794,22 +794,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-9.864043739585366</v>
+        <v>-12.56073950861472</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-22.83988672245083</v>
+        <v>-21.9675602971859</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-20.0025163841903</v>
+        <v>-18.28799742520523</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.1727318936606963</v>
+        <v>-0.2141406643044646</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.4135009773195613</v>
+        <v>-0.4040717662392801</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.3981928662649488</v>
+        <v>-0.3796803260866969</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10.14346606388379</v>
+        <v>5.943676994840732</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-3.464731914823332</v>
+        <v>-5.448450688289458</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6.301075093199633</v>
+        <v>7.587864928334355</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.2093451501930489</v>
+        <v>0.1212417784762518</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.07393440111953362</v>
+        <v>-0.1179924646348894</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1463506475196255</v>
+        <v>0.198311822112257</v>
       </c>
     </row>
     <row r="13">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-14.35951226301108</v>
+        <v>-11.89079977519611</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-7.663522930678604</v>
+        <v>-10.99039224041422</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-17.57230751240032</v>
+        <v>-18.40371785862661</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.3469170021963952</v>
+        <v>-0.2967849342670397</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.2386557515331303</v>
+        <v>-0.3244890835129133</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.5433488791702172</v>
+        <v>-0.5608431063383675</v>
       </c>
     </row>
     <row r="14">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-23.21243653102392</v>
+        <v>-20.27010808635546</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-16.619274532272</v>
+        <v>-19.69861280241998</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-30.39707156607484</v>
+        <v>-30.04061634447993</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.5059151585536504</v>
+        <v>-0.4607959635317563</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.4410763122043909</v>
+        <v>-0.5262065849410685</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.7453411786641653</v>
+        <v>-0.7478340172351193</v>
       </c>
     </row>
     <row r="15">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>-6.026714880504888</v>
+        <v>-3.931561330130769</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.9128541708607949</v>
+        <v>-2.335105777826681</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-7.279675619616619</v>
+        <v>-8.749386276343902</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.1531757562215723</v>
+        <v>-0.1081151827214802</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.03331586094325876</v>
+        <v>-0.08512912034992277</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.2513664151310048</v>
+        <v>-0.2833034056803447</v>
       </c>
     </row>
     <row r="16">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-8.646016862266686</v>
+        <v>-7.130798066898336</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-10.57482590979102</v>
+        <v>-10.88127001684109</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-13.11358105237744</v>
+        <v>-12.32099497987068</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.1610404554092529</v>
+        <v>-0.1372871967218577</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.2331172834798522</v>
+        <v>-0.2419034241351145</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.3191600958763511</v>
+        <v>-0.3000036730722092</v>
       </c>
     </row>
     <row r="17">
@@ -958,22 +958,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-14.05485157358868</v>
+        <v>-11.55818027409675</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-15.3838240810823</v>
+        <v>-15.66595578458453</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-20.59297094299193</v>
+        <v>-19.56773449867364</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.2495733593773561</v>
+        <v>-0.2154209110154637</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.3225077584074911</v>
+        <v>-0.3299600247251513</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.457093758520137</v>
+        <v>-0.433686800202977</v>
       </c>
     </row>
     <row r="18">
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>-4.067695096038559</v>
+        <v>-2.246878864561404</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-5.620049701465927</v>
+        <v>-6.128327594752905</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-6.229699311760297</v>
+        <v>-5.63538401008767</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-0.07875899032385812</v>
+        <v>-0.04450487681209975</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.1306902523445392</v>
+        <v>-0.1462447275305425</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.1605174301198594</v>
+        <v>-0.13944170009337</v>
       </c>
     </row>
     <row r="19">
